--- a/parameters/DeviceParameters_Default.xlsx
+++ b/parameters/DeviceParameters_Default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma11115\Box\github_folder\DriftFusionOPV\parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/jsm121_ic_ac_uk/Documents/Imperial PhD/03 Projects/04 Computational/DrifFusionOPV Git/parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A994A08-6C85-4E6D-B1FF-157AE9394492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7A994A08-6C85-4E6D-B1FF-157AE9394492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33EF650F-F0C8-41ED-96EB-EB766E5F0439}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="1275" windowWidth="26790" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,25 +468,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="9" max="9" width="27.88671875" customWidth="1"/>
-    <col min="10" max="10" width="24.6640625" customWidth="1"/>
-    <col min="17" max="17" width="37.21875" customWidth="1"/>
-    <col min="18" max="18" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="33.33203125" customWidth="1"/>
-    <col min="31" max="31" width="25.109375" customWidth="1"/>
-    <col min="32" max="32" width="28.77734375" customWidth="1"/>
-    <col min="33" max="33" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" customWidth="1"/>
+    <col min="10" max="10" width="24.7109375" customWidth="1"/>
+    <col min="17" max="17" width="37.28515625" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="33.28515625" customWidth="1"/>
+    <col min="31" max="31" width="25.140625" customWidth="1"/>
+    <col min="32" max="32" width="28.7109375" customWidth="1"/>
+    <col min="33" max="33" width="30.28515625" customWidth="1"/>
     <col min="34" max="34" width="30" customWidth="1"/>
-    <col min="35" max="35" width="31.5546875" customWidth="1"/>
+    <col min="35" max="35" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>23</v>
       </c>
@@ -530,7 +532,7 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -628,7 +630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -729,7 +731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -830,7 +832,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -931,7 +933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="F6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -956,7 +958,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -982,7 +984,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="P8" s="1"/>
